--- a/Experiment_4/results/Experiment_4_results.xlsx
+++ b/Experiment_4/results/Experiment_4_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="65">
   <si>
     <t>VITEK</t>
   </si>
@@ -147,6 +147,66 @@
   <si>
     <t>Tigecycline_AB</t>
   </si>
+  <si>
+    <t>Antibiotic</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Amikacin</t>
+  </si>
+  <si>
+    <t>Ampicillin-sulbactam</t>
+  </si>
+  <si>
+    <t>Aztreonam</t>
+  </si>
+  <si>
+    <t>Cefazolin</t>
+  </si>
+  <si>
+    <t>Cefepime</t>
+  </si>
+  <si>
+    <t>Ceftazidime</t>
+  </si>
+  <si>
+    <t>Ceftazidime-avibactam</t>
+  </si>
+  <si>
+    <t>Cefuroxime</t>
+  </si>
+  <si>
+    <t>Ciprofloxacin</t>
+  </si>
+  <si>
+    <t>Ertapenem</t>
+  </si>
+  <si>
+    <t>Gentamicin</t>
+  </si>
+  <si>
+    <t>Imipenem</t>
+  </si>
+  <si>
+    <t>Levofloxacin</t>
+  </si>
+  <si>
+    <t>Meropenem</t>
+  </si>
+  <si>
+    <t>Piperacillin-tazobactam</t>
+  </si>
+  <si>
+    <t>Tobramycin</t>
+  </si>
 </sst>
 </file>
 
@@ -227,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -263,7 +323,10 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -475,11 +538,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1342684080"/>
-        <c:axId val="2065153373"/>
+        <c:axId val="229051895"/>
+        <c:axId val="1578560799"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1342684080"/>
+        <c:axId val="229051895"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -535,10 +598,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2065153373"/>
+        <c:crossAx val="1578560799"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2065153373"/>
+        <c:axId val="1578560799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.5"/>
@@ -616,7 +679,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1342684080"/>
+        <c:crossAx val="229051895"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -4751,9 +4814,7 @@
       <c r="E64" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>1</v>
-      </c>
+      <c r="G64" s="4"/>
       <c r="H64" s="4" t="s">
         <v>35</v>
       </c>
@@ -4874,53 +4935,113 @@
       <c r="L68" s="12"/>
     </row>
     <row r="69">
-      <c r="B69" s="13"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
+      <c r="B69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
+      <c r="G69" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="J69" s="12"/>
       <c r="K69" s="12"/>
       <c r="L69" s="12"/>
     </row>
     <row r="70">
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
+      <c r="B70" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" s="13">
+        <f>J20</f>
+        <v>9.812074154</v>
+      </c>
+      <c r="D70" s="13">
+        <f>I20</f>
+        <v>6.625208507</v>
+      </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
+      <c r="G70" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H70" s="14">
+        <f>V20</f>
+        <v>0.4865474034</v>
+      </c>
+      <c r="I70" s="14">
+        <f>U20</f>
+        <v>0.3330154509</v>
+      </c>
       <c r="J70" s="12"/>
       <c r="K70" s="12"/>
       <c r="L70" s="12"/>
     </row>
     <row r="71">
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
+      <c r="B71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="13">
+        <f>J40</f>
+        <v>11.7711943</v>
+      </c>
+      <c r="D71" s="13">
+        <f>I40</f>
+        <v>5.510300355</v>
+      </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
+      <c r="G71" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71" s="14">
+        <f>V40</f>
+        <v>0.5619023034</v>
+      </c>
+      <c r="I71" s="14">
+        <f>U40</f>
+        <v>0.3591497112</v>
+      </c>
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
       <c r="L71" s="12"/>
     </row>
     <row r="72">
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
+      <c r="B72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C72" s="13">
+        <f>J60</f>
+        <v>6.389930325</v>
+      </c>
+      <c r="D72" s="13">
+        <f>I60</f>
+        <v>4.009377857</v>
+      </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
+      <c r="G72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H72" s="14">
+        <f>V60</f>
+        <v>1.567379538</v>
+      </c>
+      <c r="I72" s="14">
+        <f>U60</f>
+        <v>1.020104995</v>
+      </c>
       <c r="J72" s="12"/>
       <c r="K72" s="12"/>
       <c r="L72" s="12"/>
@@ -9552,6 +9673,679 @@
       <c r="V144" s="8">
         <f t="shared" si="17"/>
         <v>1.748520127</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C149" s="7">
+        <v>618.0</v>
+      </c>
+      <c r="D149" s="7">
+        <v>230.0</v>
+      </c>
+      <c r="E149" s="7">
+        <v>848.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C150" s="7">
+        <v>149.0</v>
+      </c>
+      <c r="D150" s="7">
+        <v>365.0</v>
+      </c>
+      <c r="E150" s="7">
+        <v>514.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C151" s="7">
+        <v>232.0</v>
+      </c>
+      <c r="D151" s="7">
+        <v>426.0</v>
+      </c>
+      <c r="E151" s="7">
+        <v>658.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C152" s="7">
+        <v>185.0</v>
+      </c>
+      <c r="D152" s="7">
+        <v>388.0</v>
+      </c>
+      <c r="E152" s="7">
+        <v>573.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C153" s="7">
+        <v>99.0</v>
+      </c>
+      <c r="D153" s="7">
+        <v>593.0</v>
+      </c>
+      <c r="E153" s="7">
+        <v>692.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C154" s="7">
+        <v>245.0</v>
+      </c>
+      <c r="D154" s="7">
+        <v>492.0</v>
+      </c>
+      <c r="E154" s="7">
+        <v>737.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C155" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="D155" s="7">
+        <v>338.0</v>
+      </c>
+      <c r="E155" s="7">
+        <v>468.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C156" s="7">
+        <v>161.0</v>
+      </c>
+      <c r="D156" s="7">
+        <v>487.0</v>
+      </c>
+      <c r="E156" s="7">
+        <v>648.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C157" s="7">
+        <v>84.0</v>
+      </c>
+      <c r="D157" s="7">
+        <v>764.0</v>
+      </c>
+      <c r="E157" s="7">
+        <v>848.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C158" s="7">
+        <v>230.0</v>
+      </c>
+      <c r="D158" s="7">
+        <v>580.0</v>
+      </c>
+      <c r="E158" s="7">
+        <v>810.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C159" s="7">
+        <v>426.0</v>
+      </c>
+      <c r="D159" s="7">
+        <v>422.0</v>
+      </c>
+      <c r="E159" s="7">
+        <v>848.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C160" s="7">
+        <v>102.0</v>
+      </c>
+      <c r="D160" s="7">
+        <v>503.0</v>
+      </c>
+      <c r="E160" s="7">
+        <v>605.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C161" s="7">
+        <v>186.0</v>
+      </c>
+      <c r="D161" s="7">
+        <v>393.0</v>
+      </c>
+      <c r="E161" s="7">
+        <v>579.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C162" s="7">
+        <v>295.0</v>
+      </c>
+      <c r="D162" s="7">
+        <v>553.0</v>
+      </c>
+      <c r="E162" s="7">
+        <v>848.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C163" s="7">
+        <v>226.0</v>
+      </c>
+      <c r="D163" s="7">
+        <v>467.0</v>
+      </c>
+      <c r="E163" s="7">
+        <v>693.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C164" s="7">
+        <v>266.0</v>
+      </c>
+      <c r="D164" s="7">
+        <v>426.0</v>
+      </c>
+      <c r="E164" s="7">
+        <v>692.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C166" s="7">
+        <v>1148.0</v>
+      </c>
+      <c r="D166" s="7">
+        <v>427.0</v>
+      </c>
+      <c r="E166" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C167" s="7">
+        <v>75.0</v>
+      </c>
+      <c r="D167" s="7">
+        <v>1500.0</v>
+      </c>
+      <c r="E167" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C168" s="7">
+        <v>198.0</v>
+      </c>
+      <c r="D168" s="7">
+        <v>1354.0</v>
+      </c>
+      <c r="E168" s="7">
+        <v>1552.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C169" s="7">
+        <v>66.0</v>
+      </c>
+      <c r="D169" s="7">
+        <v>1509.0</v>
+      </c>
+      <c r="E169" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C170" s="7">
+        <v>504.0</v>
+      </c>
+      <c r="D170" s="7">
+        <v>982.0</v>
+      </c>
+      <c r="E170" s="7">
+        <v>1486.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C171" s="7">
+        <v>121.0</v>
+      </c>
+      <c r="D171" s="7">
+        <v>1454.0</v>
+      </c>
+      <c r="E171" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172" s="7">
+        <v>78.0</v>
+      </c>
+      <c r="D172" s="7">
+        <v>1418.0</v>
+      </c>
+      <c r="E172" s="7">
+        <v>1496.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C173" s="7">
+        <v>145.0</v>
+      </c>
+      <c r="D173" s="7">
+        <v>1430.0</v>
+      </c>
+      <c r="E173" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C174" s="7">
+        <v>703.0</v>
+      </c>
+      <c r="D174" s="7">
+        <v>872.0</v>
+      </c>
+      <c r="E174" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C175" s="7">
+        <v>1155.0</v>
+      </c>
+      <c r="D175" s="7">
+        <v>420.0</v>
+      </c>
+      <c r="E175" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C176" s="7">
+        <v>306.0</v>
+      </c>
+      <c r="D176" s="7">
+        <v>1269.0</v>
+      </c>
+      <c r="E176" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C177" s="7">
+        <v>1575.0</v>
+      </c>
+      <c r="D177" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E177" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C178" s="7">
+        <v>248.0</v>
+      </c>
+      <c r="D178" s="7">
+        <v>1327.0</v>
+      </c>
+      <c r="E178" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C179" s="7">
+        <v>528.0</v>
+      </c>
+      <c r="D179" s="7">
+        <v>1047.0</v>
+      </c>
+      <c r="E179" s="7">
+        <v>1575.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C181" s="7">
+        <v>537.0</v>
+      </c>
+      <c r="D181" s="7">
+        <v>321.0</v>
+      </c>
+      <c r="E181" s="7">
+        <v>858.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C182" s="7">
+        <v>84.0</v>
+      </c>
+      <c r="D182" s="7">
+        <v>741.0</v>
+      </c>
+      <c r="E182" s="7">
+        <v>825.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C183" s="7">
+        <v>131.0</v>
+      </c>
+      <c r="D183" s="7">
+        <v>620.0</v>
+      </c>
+      <c r="E183" s="7">
+        <v>751.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C184" s="7">
+        <v>22.0</v>
+      </c>
+      <c r="D184" s="7">
+        <v>230.0</v>
+      </c>
+      <c r="E184" s="7">
+        <v>252.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C185" s="7">
+        <v>133.0</v>
+      </c>
+      <c r="D185" s="7">
+        <v>718.0</v>
+      </c>
+      <c r="E185" s="7">
+        <v>851.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C186" s="7">
+        <v>356.0</v>
+      </c>
+      <c r="D186" s="7">
+        <v>1374.0</v>
+      </c>
+      <c r="E186" s="7">
+        <v>1730.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C187" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="D187" s="7">
+        <v>51.0</v>
+      </c>
+      <c r="E187" s="7">
+        <v>181.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C188" s="7">
+        <v>454.0</v>
+      </c>
+      <c r="D188" s="7">
+        <v>759.0</v>
+      </c>
+      <c r="E188" s="7">
+        <v>1213.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C189" s="7">
+        <v>159.0</v>
+      </c>
+      <c r="D189" s="7">
+        <v>914.0</v>
+      </c>
+      <c r="E189" s="7">
+        <v>1073.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C190" s="7">
+        <v>32.0</v>
+      </c>
+      <c r="D190" s="7">
+        <v>471.0</v>
+      </c>
+      <c r="E190" s="7">
+        <v>503.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C191" s="7">
+        <v>564.0</v>
+      </c>
+      <c r="D191" s="7">
+        <v>485.0</v>
+      </c>
+      <c r="E191" s="7">
+        <v>1049.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C192" s="7">
+        <v>612.0</v>
+      </c>
+      <c r="D192" s="7">
+        <v>277.0</v>
+      </c>
+      <c r="E192" s="7">
+        <v>889.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C193" s="7">
+        <v>261.0</v>
+      </c>
+      <c r="D193" s="7">
+        <v>330.0</v>
+      </c>
+      <c r="E193" s="7">
+        <v>591.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C194" s="7">
+        <v>622.0</v>
+      </c>
+      <c r="D194" s="7">
+        <v>316.0</v>
+      </c>
+      <c r="E194" s="7">
+        <v>938.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C195" s="7">
+        <v>308.0</v>
+      </c>
+      <c r="D195" s="7">
+        <v>500.0</v>
+      </c>
+      <c r="E195" s="7">
+        <v>808.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C196" s="7">
+        <v>209.0</v>
+      </c>
+      <c r="D196" s="7">
+        <v>374.0</v>
+      </c>
+      <c r="E196" s="7">
+        <v>583.0</v>
       </c>
     </row>
   </sheetData>
